--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Термодинамика процесса гидролиза\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LebedevaMA\myproject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{6C90F930-1523-4A5D-A958-51E67B86D67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D0D958-9B41-40C7-B051-70F5C6784F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="4" activeTab="9" xr2:uid="{FD136DF5-4842-47DF-A83D-B3DEBC69E81C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="4" activeTab="4" xr2:uid="{FD136DF5-4842-47DF-A83D-B3DEBC69E81C}"/>
   </bookViews>
   <sheets>
     <sheet name="Experimental_sol_Mg_SO4" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <sheet name="References" sheetId="1" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
